--- a/forms/trg/Formulir_TRG_prepodyreg.xlsx
+++ b/forms/trg/Formulir_TRG_prepodyreg.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
